--- a/app/reports/DXYZ_research.xlsx
+++ b/app/reports/DXYZ_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-11 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>32.305</v>
+        <v>32.435</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0492199993133545</v>
+        <v>0.04947000026702881</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>30465664.13867822</v>
+        <v>30465665.36149221</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>32.305</v>
+        <v>32.435</v>
       </c>
     </row>
     <row r="38">
@@ -1493,10 +1493,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>984193280</v>
+        <v>988153856</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="E5" s="31" t="n"/>
       <c r="F5" s="31" t="n"/>
@@ -1553,12 +1553,12 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>232812384</v>
+        <v>231523536</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n"/>
       <c r="F8" s="33" t="n">
-        <v>4.878</v>
+        <v>4.795</v>
       </c>
     </row>
     <row r="9">
@@ -1589,12 +1589,12 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>82644008</v>
+        <v>83060704</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="33" t="n">
-        <v>5.55</v>
+        <v>5.569</v>
       </c>
     </row>
     <row r="11">
@@ -1609,14 +1609,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>324444128</v>
+        <v>326455136</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>13.081081</v>
+        <v>13.162162</v>
       </c>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n">
-        <v>6.748</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="12">
@@ -1649,16 +1649,16 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>352682592</v>
+        <v>351527200</v>
       </c>
       <c r="D13" s="33" t="n">
-        <v>5.5248866</v>
+        <v>5.5067873</v>
       </c>
       <c r="E13" s="33" t="n">
-        <v>2.484</v>
+        <v>2.486</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>1.435</v>
+        <v>1.437</v>
       </c>
     </row>
     <row r="15">
